--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487800_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487800_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.8612</v>
+        <v>10.5835</v>
       </c>
       <c r="E2" t="n">
-        <v>11.8998</v>
+        <v>12.3284</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0385</v>
+        <v>-1.7449</v>
       </c>
       <c r="G2" t="n">
         <v>8.5945</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2983</v>
+        <v>-0.576</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6524</v>
+        <v>-0.2238</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6458</v>
+        <v>-0.3522</v>
       </c>
       <c r="V2" t="n">
         <v>2.565</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4306</v>
+        <v>4.2306</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6118</v>
+        <v>7.1476</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.1812</v>
+        <v>-2.917</v>
       </c>
       <c r="G3" t="n">
         <v>5.5378</v>
@@ -688,13 +688,13 @@
         <v>0.4162</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7992</v>
+        <v>0.0008</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2486</v>
+        <v>0.2872</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5506</v>
+        <v>-0.2864</v>
       </c>
       <c r="V3" t="n">
         <v>1.3975</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7041</v>
+        <v>2.4222</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2729</v>
+        <v>1.8443</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4311</v>
+        <v>0.5779</v>
       </c>
       <c r="G4" t="n">
         <v>-1.9451</v>
@@ -766,13 +766,13 @@
         <v>0.6244</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1507</v>
+        <v>-0.1311</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6458</v>
+        <v>0.2172</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4951</v>
+        <v>-0.3483</v>
       </c>
       <c r="V4" t="n">
         <v>3.8741</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7712</v>
+        <v>0.4893</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5118</v>
+        <v>1.0832</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7407</v>
+        <v>-0.5939</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5595</v>
@@ -844,13 +844,13 @@
         <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7875</v>
+        <v>0.5056</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.5558</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.197</v>
+        <v>-0.0502</v>
       </c>
       <c r="V5" t="n">
         <v>1.1675</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ORENGA IMAZ</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4805</v>
+        <v>-0.4678</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4683</v>
+        <v>0.7464</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9878</v>
+        <v>-1.2142</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9081</v>
+        <v>-0.078</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9082</v>
+        <v>0.3049</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0001</v>
+        <v>-0.3829</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2229</v>
+        <v>1.057</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5609</v>
+        <v>0.9786</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.0784</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.131</v>
+        <v>-1.1349</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3473</v>
+        <v>-0.6737</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2164</v>
+        <v>-0.4613</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0406</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q6" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.0406</v>
-      </c>
       <c r="S6" t="n">
-        <v>1.5155</v>
+        <v>0.6508</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2454</v>
+        <v>0.5001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2701</v>
+        <v>0.1507</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>P. ORENGA IMAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4296</v>
+        <v>-0.4751</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9607</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3903</v>
+        <v>-1.1933</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.078</v>
+        <v>-0.9081</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3049</v>
+        <v>-1.9082</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3829</v>
+        <v>1.0001</v>
       </c>
       <c r="J7" t="n">
-        <v>1.057</v>
+        <v>0.2229</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9786</v>
+        <v>-0.5609</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0784</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1349</v>
+        <v>-1.131</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6737</v>
+        <v>-1.3473</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4613</v>
+        <v>0.2164</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0406</v>
+        <v>1.0406</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>1.0406</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.5599</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.4953</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1.1675</v>
+      </c>
+      <c r="W7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="n">
-        <v>0.6889</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.7144</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.0254</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.23</v>
-      </c>
       <c r="X7" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5907</v>
+        <v>-0.8931</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1497</v>
+        <v>-0.3641</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.441</v>
+        <v>-0.5291</v>
       </c>
       <c r="G8" t="n">
         <v>-0.914</v>
@@ -1078,13 +1078,13 @@
         <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5532</v>
+        <v>0.2509</v>
       </c>
       <c r="T8" t="n">
-        <v>0.531</v>
+        <v>0.3167</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0222</v>
+        <v>-0.0659</v>
       </c>
       <c r="V8" t="n">
         <v>-0.23</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.128</v>
+        <v>-1.9205</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6831</v>
+        <v>-2.3885</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.8111</v>
+        <v>0.468</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6207</v>
+        <v>-0.1115</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0808</v>
+        <v>0.949</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7014</v>
+        <v>-1.0605</v>
       </c>
       <c r="J9" t="n">
-        <v>1.87</v>
+        <v>0.4194</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1727</v>
+        <v>1.0554</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6973</v>
+        <v>-0.636</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2494</v>
+        <v>-0.5308</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2535</v>
+        <v>-0.1063</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0041</v>
+        <v>-0.4245</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4162</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0026</v>
+        <v>0.2098</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3138</v>
+        <v>-0.3729</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3165</v>
+        <v>0.5826</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.3351</v>
+        <v>-0.3538</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1675</v>
+        <v>-0.3538</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.5026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1935</v>
+        <v>-2.0311</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6028</v>
+        <v>1.8974</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4093</v>
+        <v>-3.9286</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1115</v>
+        <v>0.6207</v>
       </c>
       <c r="H10" t="n">
-        <v>0.949</v>
+        <v>-1.0808</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0605</v>
+        <v>1.7014</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4194</v>
+        <v>1.87</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0554</v>
+        <v>0.1727</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.636</v>
+        <v>1.6973</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5308</v>
+        <v>-1.2494</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1063</v>
+        <v>-1.2535</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4245</v>
+        <v>0.0041</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6649</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0633</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5239</v>
+        <v>0.199</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3538</v>
+        <v>-2.3351</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3538</v>
+        <v>1.1675</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-3.5026</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0957</v>
+        <v>-3.128</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0769</v>
+        <v>-0.434</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0188</v>
+        <v>-2.6941</v>
       </c>
       <c r="G11" t="n">
         <v>0.0094</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5598</v>
+        <v>0.5275</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7829</v>
+        <v>-0.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3428</v>
+        <v>0.6675</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1675</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.810099999999998</v>
+        <v>8.81</v>
       </c>
       <c r="E12" t="n">
-        <v>22.579</v>
+        <v>22.5789</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.769</v>
+        <v>-13.7692</v>
       </c>
       <c r="G12" t="n">
         <v>10.2462</v>
@@ -1375,7 +1375,7 @@
         <v>-15.2286</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.207699999999999</v>
+        <v>-9.207700000000001</v>
       </c>
       <c r="O12" t="n">
         <v>-6.020899999999999</v>
@@ -1387,31 +1387,31 @@
         <v>-14.5684</v>
       </c>
       <c r="R12" t="n">
-        <v>7.284199999999999</v>
+        <v>7.284199999999998</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0974</v>
+        <v>2.0977</v>
       </c>
       <c r="T12" t="n">
         <v>1.5361</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5616000000000001</v>
+        <v>0.5613999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>3.7502</v>
+        <v>3.750199999999998</v>
       </c>
       <c r="W12" t="n">
         <v>10.1363</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.386100000000001</v>
+        <v>-6.3861</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>J. BERGENS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8079</v>
+        <v>3.5176</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6274</v>
+        <v>5.6332</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1805</v>
+        <v>-2.1156</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.589</v>
+        <v>1.2688</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0568</v>
+        <v>0.3602</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6458</v>
+        <v>0.9087</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1587</v>
+        <v>4.988</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8452</v>
+        <v>2.1934</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3135</v>
+        <v>2.7946</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.7477</v>
+        <v>-3.7192</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.7884</v>
+        <v>-1.8332</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9593</v>
+        <v>-1.8859</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2893</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2893</v>
+        <v>1.6649</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5274</v>
+        <v>-0.2502</v>
       </c>
       <c r="T13" t="n">
-        <v>1.655</v>
+        <v>-0.2985</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8724</v>
+        <v>0.0483</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5802</v>
+        <v>2.9153</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8137</v>
+        <v>3.0249</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2335</v>
+        <v>-0.1097</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. BERGENS</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9843</v>
+        <v>3.0126</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4189</v>
+        <v>3.4487</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4346</v>
+        <v>-0.4361</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2688</v>
+        <v>-0.589</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3602</v>
+        <v>0.0568</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9087</v>
+        <v>-0.6458</v>
       </c>
       <c r="J14" t="n">
-        <v>4.988</v>
+        <v>2.1587</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1934</v>
+        <v>1.8452</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7946</v>
+        <v>0.3135</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.7192</v>
+        <v>-2.7477</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8332</v>
+        <v>-1.7884</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8859</v>
+        <v>-0.9593</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4162</v>
+        <v>2.2893</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6649</v>
+        <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7836</v>
+        <v>0.7321</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5129</v>
+        <v>0.4763</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2707</v>
+        <v>0.2558</v>
       </c>
       <c r="V14" t="n">
-        <v>2.9153</v>
+        <v>0.5802</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0249</v>
+        <v>0.8137</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1097</v>
+        <v>-0.2335</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6876</v>
+        <v>1.7526</v>
       </c>
       <c r="E15" t="n">
-        <v>3.757</v>
+        <v>3.6498</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0694</v>
+        <v>-1.8972</v>
       </c>
       <c r="G15" t="n">
         <v>-1.0211</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3549</v>
+        <v>0.42</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5401</v>
+        <v>0.433</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1852</v>
+        <v>-0.013</v>
       </c>
       <c r="V15" t="n">
         <v>1.5213</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4538</v>
+        <v>-0.1514</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8305</v>
+        <v>3.0448</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.2843</v>
+        <v>-3.1962</v>
       </c>
       <c r="G16" t="n">
         <v>0.4295</v>
@@ -1702,13 +1702,13 @@
         <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6061</v>
+        <v>-0.3037</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3791</v>
+        <v>-0.1648</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.227</v>
+        <v>-0.139</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6934</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8165</v>
+        <v>-0.4363</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9693000000000001</v>
+        <v>1.2907</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7858</v>
+        <v>-1.7271</v>
       </c>
       <c r="G17" t="n">
         <v>1.2804</v>
@@ -1780,13 +1780,13 @@
         <v>0.2081</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4299</v>
+        <v>-0.0498</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1833</v>
+        <v>0.1381</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2466</v>
+        <v>-0.1879</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8751</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3649</v>
+        <v>-0.8404</v>
       </c>
       <c r="E18" t="n">
         <v>2.6077</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.9726</v>
+        <v>-3.4481</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5322</v>
@@ -1858,13 +1858,13 @@
         <v>2.4974</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.389</v>
+        <v>-0.8645</v>
       </c>
       <c r="T18" t="n">
         <v>-0.6433</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7457</v>
+        <v>-0.2211</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9411</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.582</v>
+        <v>-1.6114</v>
       </c>
       <c r="E19" t="n">
         <v>-0.19</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.392</v>
+        <v>-1.4213</v>
       </c>
       <c r="G19" t="n">
         <v>-0.432</v>
@@ -1936,13 +1936,13 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3582</v>
+        <v>-0.3875</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3791</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0209</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5838</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0553</v>
+        <v>-2.8792</v>
       </c>
       <c r="E20" t="n">
         <v>-0.9829</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0724</v>
+        <v>-1.8962</v>
       </c>
       <c r="G20" t="n">
         <v>-3.4986</v>
@@ -2014,13 +2014,13 @@
         <v>2.0812</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2369</v>
+        <v>-0.0607</v>
       </c>
       <c r="T20" t="n">
         <v>0.3601</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5969</v>
+        <v>-0.4208</v>
       </c>
       <c r="V20" t="n">
         <v>-1.401</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6672</v>
+        <v>-3.495</v>
       </c>
       <c r="E21" t="n">
         <v>-1.6781</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9891</v>
+        <v>-1.8169</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0409</v>
@@ -2092,13 +2092,13 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4619</v>
+        <v>-0.2897</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1957</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2662</v>
+        <v>-0.0939</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7076</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.35</v>
+        <v>-6.965</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5908</v>
+        <v>-3.055</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.7592</v>
+        <v>-3.91</v>
       </c>
       <c r="G22" t="n">
         <v>-5.1112</v>
@@ -2170,13 +2170,13 @@
         <v>2.0812</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7144</v>
+        <v>-0.3293</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8234</v>
+        <v>-0.2876</v>
       </c>
       <c r="U22" t="n">
-        <v>0.109</v>
+        <v>-0.0417</v>
       </c>
       <c r="V22" t="n">
         <v>-2.565</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.809899999999999</v>
+        <v>-8.0959</v>
       </c>
       <c r="E23" t="n">
-        <v>13.769</v>
+        <v>13.7689</v>
       </c>
       <c r="F23" t="n">
-        <v>-22.5789</v>
+        <v>-21.8647</v>
       </c>
       <c r="G23" t="n">
         <v>-10.2463</v>
@@ -2248,13 +2248,13 @@
         <v>14.5683</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.097699999999999</v>
+        <v>-1.3833</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5615999999999999</v>
+        <v>-0.5615000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.536</v>
+        <v>-0.8218</v>
       </c>
       <c r="V23" t="n">
         <v>-3.7502</v>
